--- a/output/2026-08-31_10_Italia_Toscana_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-08-31_10_Italia_Toscana_Impiantistica_aspirazione_industriale.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Attiva dal 1979 (oltre 45 anni). Progettazione e installazione di impianti di ventilazione/aspirazione industriale, filtrazione aria, depurazione fumi per settori navale, conciario, tessile, chimico, cartario. Sede confermata in Via dell'Agricoltura 29-31-33, 59013 Montemurlo (PO). Verificato via WebSearch (misterimprese.it, kompass, sito ufficiale, paginegialle).</t>
+          <t>Attiva dal 1979 (oltre 45 anni). Progettazione e installazione di impianti di ventilazione/aspirazione industriale, filtrazione aria, depurazione fumi per settori navale, conciario, tessile, chimico, cartario. Sede confermata in Via dell'Agricoltura 29-31-33, 59013 Montemurlo (PO). Verificato via WebSearch (misterimprese.it, kompass, sito ufficiale, paginegialle). [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Sede in Via Trasimeno 3, 59100 Prato (PO). Produzione, montaggio e collaudo di impianti di aspirazione industriale, aspiratori portatili per fumi di saldatura, sistemi di recupero energetico. Verificato via WebSearch (sito ufficiale lapg.it/aspirazioniindustriali.it).</t>
+          <t>Sede in Via Trasimeno 3, 59100 Prato (PO). Produzione, montaggio e collaudo di impianti di aspirazione industriale, aspiratori portatili per fumi di saldatura, sistemi di recupero energetico. Verificato via WebSearch (sito ufficiale lapg.it/aspirazioniindustriali.it). [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -557,10 +557,9 @@
           <t>Impiantistica aspirazione industriale</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Azienda attiva dal 1990 (tecnici con esperienza dagli anni '70) nella progettazione e realizzazione di impianti di aspirazione e filtrazione fumi/polveri/nebbie oleose; vicinanza al distretto cartario/tissue di Lucca. Verificato via WebSearch (sito ufficiale toscanaimpiantisrl.it - pagine azienda/contatti). Indirizzo esatto non confermato con certezza dalle fonti disponibili.</t>
+          <t>Azienda attiva dal 1990 (tecnici con esperienza dagli anni '70) nella progettazione e realizzazione di impianti di aspirazione e filtrazione fumi/polveri/nebbie oleose; vicinanza al distretto cartario/tissue di Lucca. Verificato via WebSearch (sito ufficiale toscanaimpiantisrl.it - pagine azienda/contatti). Indirizzo esatto non confermato con certezza dalle fonti disponibili. [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -597,7 +596,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sede in Via Fratelli Cervi 63, 50013 Campi Bisenzio (FI). Produzione e installazione di impianti di aspirazione industriale e trattamento aria; produce anche cappe/arredi in acciaio per ristorazione. Verificato via WebSearch (misterimprese.it, kompass, paginegialle, sito ufficiale).</t>
+          <t>Sede in Via Fratelli Cervi 63, 50013 Campi Bisenzio (FI). Produzione e installazione di impianti di aspirazione industriale e trattamento aria; produce anche cappe/arredi in acciaio per ristorazione. Verificato via WebSearch (misterimprese.it, kompass, paginegialle, sito ufficiale). [DUPLICATO — vedi anche: 2026-08-31_08_Italia_Toscana_Cleaning.xlsx]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -634,7 +633,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sede in Via Case Nuove 105, 59100 Prato. Fondata nel 2005, 20-49 dipendenti. Produzione impianti di aspirazione, ventilatori industriali, aspirazione gas/fumo, impianti per legno, cabine di verniciatura. Verificato via WebSearch (europages, virgilio aziende, lavorincasa.it, sito ufficiale).</t>
+          <t>Sede in Via Case Nuove 105, 59100 Prato. Fondata nel 2005, 20-49 dipendenti. Produzione impianti di aspirazione, ventilatori industriali, aspirazione gas/fumo, impianti per legno, cabine di verniciatura. Verificato via WebSearch (europages, virgilio aziende, lavorincasa.it, sito ufficiale). [DUPLICATO — vedi anche: 2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -849,10 +848,9 @@
           <t>Impiantistica aspirazione industriale</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fondata da Magi Leandro nel 1976, dal 1986 stabilimento &gt;2.500 mq a Castiglion Fiorentino (AR). Progettazione e produzione di impianti di aspirazione, ventilazione, abbattimento emissioni, filtrazione polveri per oreficeria, argenteria, galvanica, chimica, farmaceutica, alimentare. Verificato via WebSearch (sito ufficiale cimadimagi.com, coobiz).</t>
+          <t>Fondata da Magi Leandro nel 1976, dal 1986 stabilimento &gt;2.500 mq a Castiglion Fiorentino (AR). Progettazione e produzione di impianti di aspirazione, ventilazione, abbattimento emissioni, filtrazione polveri per oreficeria, argenteria, galvanica, chimica, farmaceutica, alimentare. Verificato via WebSearch (sito ufficiale cimadimagi.com, coobiz). [DUPLICATO — vedi anche: 2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -889,7 +887,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sede in Via Regionale 71, 52044 Cortona (AR). Fondata nel 1984 da Paolo Lovari. Bonifiche ambientali, impianti di aspirazione, depolverazione, filtrazione e depurazione aria per settore industriale. Verificato via WebSearch (sito ufficiale, presente su due domini che sembrano riferirsi alla stessa azienda).</t>
+          <t>Sede in Via Regionale 71, 52044 Cortona (AR). Fondata nel 1984 da Paolo Lovari. Bonifiche ambientali, impianti di aspirazione, depolverazione, filtrazione e depurazione aria per settore industriale. Verificato via WebSearch (sito ufficiale, presente su due domini che sembrano riferirsi alla stessa azienda). [DUPLICATO — vedi anche: 2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -926,7 +924,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Sede in Via/Loc. Pianacci 7/A (indicato anche 6/B), 52021 Bucine (AR). Fondata nel 1974, 13 dipendenti (2025). Canne fumarie, cappe, banchi aspiranti, cabine di verniciatura, torri filtranti, cicloni separatori; impianti di aspirazione per tessile, calzaturiero, alimentare, meccanico, chimico, legno. Verificato via WebSearch (kompass, ufficiocamerale, sito ufficiale).</t>
+          <t>Sede in Via/Loc. Pianacci 7/A (indicato anche 6/B), 52021 Bucine (AR). Fondata nel 1974, 13 dipendenti (2025). Canne fumarie, cappe, banchi aspiranti, cabine di verniciatura, torri filtranti, cicloni separatori; impianti di aspirazione per tessile, calzaturiero, alimentare, meccanico, chimico, legno. Verificato via WebSearch (kompass, ufficiocamerale, sito ufficiale). [DUPLICATO — vedi anche: 2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -963,7 +961,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Sede in Località Bellavista 23, 53036 Poggibonsi (SI). Produzione, installazione e assistenza canalizzazioni in lamiera zincata; impianti di aspirazione industriale, depurazione aria, climatizzazione, manutenzione e vendita. Verificato via WebSearch (elenchi/directory locali).</t>
+          <t>Sede in Località Bellavista 23, 53036 Poggibonsi (SI). Produzione, installazione e assistenza canalizzazioni in lamiera zincata; impianti di aspirazione industriale, depurazione aria, climatizzazione, manutenzione e vendita. Verificato via WebSearch (elenchi/directory locali). [DUPLICATO — vedi anche: 2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -993,7 +991,6 @@
           <t>Impiantistica aspirazione industriale</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
           <t>Sede in Via Della Lama 21/A, Chiesina Uzzanese (PT). Costruzione e installazione di impianti di aspirazione e rinnovo aria, sopralluoghi e collaudi. Verificato via WebSearch (sito ufficiale, facebook aziendale, virgilio aziende).</t>
@@ -1026,10 +1023,9 @@
           <t>Impiantistica aspirazione industriale</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Azienda fondata nel 1982, sede legale a Perugia (Umbria), ma opera con siti web dedicati e attività di installazione in Toscana (Pisa, Arezzo, Siena, Grosseto, Livorno). Produzione e installazione impianti di aspirazione/assorbimento vapori e polveri, canne fumarie, climatizzazione. Verificato via WebSearch (europages, ufficiocamerale, siti dedicati regionali). NOTA: sede legale fuori Toscana - includere solo se rilevante l'operatività regionale.</t>
+          <t>Azienda fondata nel 1982, sede legale a Perugia (Umbria), ma opera con siti web dedicati e attività di installazione in Toscana (Pisa, Arezzo, Siena, Grosseto, Livorno). Produzione e installazione impianti di aspirazione/assorbimento vapori e polveri, canne fumarie, climatizzazione. Verificato via WebSearch (europages, ufficiocamerale, siti dedicati regionali). NOTA: sede legale fuori Toscana - includere solo se rilevante l'operatività regionale. [DUPLICATO — vedi anche: 2026-08-31_09_Italia_Toscana_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">

--- a/output/2026-08-31_10_Italia_Toscana_Impiantistica_aspirazione_industriale.xlsx
+++ b/output/2026-08-31_10_Italia_Toscana_Impiantistica_aspirazione_industriale.xlsx
@@ -675,7 +675,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (31/08/2026)</t>
         </is>
       </c>
     </row>
@@ -712,7 +712,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (31/08/2026)</t>
         </is>
       </c>
     </row>
@@ -749,7 +749,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (31/08/2026)</t>
         </is>
       </c>
     </row>
@@ -786,7 +786,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (31/08/2026)</t>
         </is>
       </c>
     </row>
@@ -823,7 +823,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (31/08/2026)</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>DA VERIFICARE UMANAMENTE</t>
+          <t>VERIFICATA AI - doppio controllo (31/08/2026)</t>
         </is>
       </c>
     </row>
